--- a/data/door.xlsx
+++ b/data/door.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="8_{8E56100C-6060-4B06-93B2-092395E12ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CB580A9-6072-4BC5-8DB4-61041A85E4B0}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="8_{8E56100C-6060-4B06-93B2-092395E12ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C9443FD-03E7-4481-98F8-FBC3D6576E57}"/>
   <bookViews>
-    <workbookView xWindow="4485" yWindow="900" windowWidth="7725" windowHeight="13710" tabRatio="673" firstSheet="24" activeTab="25" xr2:uid="{3EFBE4C7-CD44-47EF-BD87-A121CAFEE801}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="673" firstSheet="24" activeTab="25" xr2:uid="{3EFBE4C7-CD44-47EF-BD87-A121CAFEE801}"/>
   </bookViews>
   <sheets>
     <sheet name="バギー一味冒険記" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="1422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="1423">
   <si>
     <t>バギー一味のその後</t>
     <rPh sb="3" eb="5">
@@ -5884,6 +5884,10 @@
     <rPh sb="7" eb="12">
       <t>キンイナリダイサン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>帰ってびっくり森番長の大仕事</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8323,7 +8327,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" ht="168.75" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>175</v>
       </c>
@@ -9840,7 +9844,7 @@
         <v>516</v>
       </c>
       <c r="B213" t="s">
-        <v>517</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.4">
